--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-08-2025.xlsx
@@ -589,29 +589,29 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -710,29 +710,29 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -831,29 +831,29 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -952,29 +952,29 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1073,29 +1073,29 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1194,29 +1194,29 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1315,29 +1315,29 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1436,29 +1436,29 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1557,29 +1557,29 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1678,29 +1678,29 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1799,29 +1799,29 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1920,29 +1920,29 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2041,29 +2041,29 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2162,29 +2162,29 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2283,29 +2283,29 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,29 +2501,29 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -2622,29 +2622,29 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2743,29 +2743,29 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -2864,29 +2864,29 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2985,29 +2985,29 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -3106,29 +3106,29 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3227,29 +3227,29 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3348,29 +3348,29 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -3469,29 +3469,29 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=139.0.7258.68); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.128); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c0b46b25+79621]
-	GetHandleVerifier [0x0x7ff7c0b46b80+79712]
-	(No symbol) [0x0x7ff7c08dc0ea]
-	(No symbol) [0x0x7ff7c0932f56]
-	(No symbol) [0x0x7ff7c093320c]
-	(No symbol) [0x0x7ff7c09865b7]
-	(No symbol) [0x0x7ff7c095b17f]
-	(No symbol) [0x0x7ff7c09833d0]
-	(No symbol) [0x0x7ff7c095af13]
-	(No symbol) [0x0x7ff7c0924151]
-	(No symbol) [0x0x7ff7c0924ee3]
-	GetHandleVerifier [0x0x7ff7c0e0683d+2962461]
-	GetHandleVerifier [0x0x7ff7c0e00b5d+2938685]
-	GetHandleVerifier [0x0x7ff7c0e1f71d+3064573]
-	GetHandleVerifier [0x0x7ff7c0b60c6e+186446]
-	GetHandleVerifier [0x0x7ff7c0b68a3f+218655]
-	GetHandleVerifier [0x0x7ff7c0b4f914+115956]
-	GetHandleVerifier [0x0x7ff7c0b4fac9+116393]
-	GetHandleVerifier [0x0x7ff7c0b35ef8+10968]
-	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
-	RtlUserThreadStart [0x0x7ff9a473c34c+44]
+	GetHandleVerifier [0x0x7ff77ce26b25+79621]
+	GetHandleVerifier [0x0x7ff77ce26b80+79712]
+	(No symbol) [0x0x7ff77cbbc0ea]
+	(No symbol) [0x0x7ff77cc12f56]
+	(No symbol) [0x0x7ff77cc1320c]
+	(No symbol) [0x0x7ff77cc665b7]
+	(No symbol) [0x0x7ff77cc3b17f]
+	(No symbol) [0x0x7ff77cc633d0]
+	(No symbol) [0x0x7ff77cc3af13]
+	(No symbol) [0x0x7ff77cc04151]
+	(No symbol) [0x0x7ff77cc04ee3]
+	GetHandleVerifier [0x0x7ff77d0e683d+2962461]
+	GetHandleVerifier [0x0x7ff77d0e0b5d+2938685]
+	GetHandleVerifier [0x0x7ff77d0ff71d+3064573]
+	GetHandleVerifier [0x0x7ff77ce40c6e+186446]
+	GetHandleVerifier [0x0x7ff77ce48a3f+218655]
+	GetHandleVerifier [0x0x7ff77ce2f914+115956]
+	GetHandleVerifier [0x0x7ff77ce2fac9+116393]
+	GetHandleVerifier [0x0x7ff77ce15ef8+10968]
+	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
+	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
 </t>
         </is>
       </c>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.windwarrior.com/about-honor/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
